--- a/outputs/evaluation/decision/v2/CF_M05/run_2/CF_M05_decision_eval.xlsx
+++ b/outputs/evaluation/decision/v2/CF_M05/run_2/CF_M05_decision_eval.xlsx
@@ -450,13 +450,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.6667</v>
+        <v>0.5</v>
       </c>
       <c r="C2" t="n">
-        <v>0.3077</v>
+        <v>0.3846</v>
       </c>
       <c r="D2" t="n">
-        <v>0.8757</v>
+        <v>0.8588</v>
       </c>
     </row>
     <row r="5">
@@ -513,10 +513,10 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="D7" t="n">
-        <v>0.9247</v>
+        <v>0.9428</v>
       </c>
     </row>
     <row r="8">
@@ -531,7 +531,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.75</v>
+        <v>0.6</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -582,7 +582,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4">
@@ -592,7 +592,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5">
@@ -602,7 +602,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6">
@@ -612,7 +612,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="7">
@@ -622,7 +622,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.6667</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="8">
@@ -632,7 +632,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.3077</v>
+        <v>0.3846</v>
       </c>
     </row>
     <row r="9">
@@ -726,19 +726,19 @@
         <v>13</v>
       </c>
       <c r="C2" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
@@ -755,28 +755,28 @@
         <v>13</v>
       </c>
       <c r="C3" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I3" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="J3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
@@ -792,31 +792,31 @@
         <v>13</v>
       </c>
       <c r="C4" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D4" t="n">
+        <v>5</v>
+      </c>
+      <c r="E4" t="n">
+        <v>5</v>
+      </c>
+      <c r="F4" t="n">
         <v>4</v>
       </c>
-      <c r="E4" t="n">
+      <c r="G4" t="n">
+        <v>5</v>
+      </c>
+      <c r="H4" t="n">
+        <v>5</v>
+      </c>
+      <c r="I4" t="n">
+        <v>5</v>
+      </c>
+      <c r="J4" t="n">
+        <v>7</v>
+      </c>
+      <c r="K4" t="n">
         <v>4</v>
-      </c>
-      <c r="F4" t="n">
-        <v>3</v>
-      </c>
-      <c r="G4" t="n">
-        <v>4</v>
-      </c>
-      <c r="H4" t="n">
-        <v>4</v>
-      </c>
-      <c r="I4" t="n">
-        <v>4</v>
-      </c>
-      <c r="J4" t="n">
-        <v>6</v>
-      </c>
-      <c r="K4" t="n">
-        <v>3</v>
       </c>
     </row>
     <row r="5">
@@ -829,22 +829,22 @@
         <v>13</v>
       </c>
       <c r="C5" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F5" t="n">
         <v>3</v>
       </c>
       <c r="G5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
@@ -861,7 +861,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U5"/>
+  <dimension ref="A1:U6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -974,22 +974,22 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AD_06</t>
+          <t>AD_02</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>CF_M05_AD13</t>
+          <t>CF_M05_AD06</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.8097</v>
+        <v>0.8214</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F2" t="n">
         <v>1</v>
@@ -1003,72 +1003,74 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J2" t="n">
         <v>1</v>
       </c>
       <c r="K2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L2" t="n">
-        <v>1</v>
-      </c>
-      <c r="M2" t="n">
-        <v>0.774</v>
+        <v>0</v>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>AWS is a consolidated cloud platform with robust services and a reliable infrastructure, and its wide selection of services makes it easy to adapt to the project's needs, allowing it to grow and scale in an agile way.</t>
+          <t>It offers flexibility, scalability, and cost reduction, as it eliminates the need for local infrastructure.</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>Amazon Web Services (AWS)</t>
+          <t>Technology cloud</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>AU_17</t>
+          <t>AU_17, AU_18, AU_19</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>9</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>This diversity makes it easy to adapt to the needs of the project, allows the project to grow and scale in an agile manner and eliminates the need to look for other platforms when requirements evolve.</t>
+          <t>The use of this type of architecture allows high scalability, availability and accessibility, since resource management can be done according to needs and anywhere with an Internet connection. It also reduces maintainability, managed by resource providers, and without major expenses, since you pay for the resources consumed.</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>*CF_M05_C18</t>
+          <t>CF_M05_C06, CF_M05_C07, CF_M05_C08, *CF_M05_C18</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>CF_M05_AU07</t>
+          <t>CF_M05_P05</t>
         </is>
       </c>
       <c r="U2" t="n">
-        <v>82</v>
+        <v>60</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AD_01</t>
+          <t>AD_08</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>CF_M05_AD01</t>
+          <t>CF_M05_AD08</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.857</v>
+        <v>0.8477</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -1077,11 +1079,13 @@
         <v>3</v>
       </c>
       <c r="F3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G3" t="n">
         <v>0</v>
       </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="H3" t="inlineStr">
         <is>
           <t>-</t>
@@ -1104,62 +1108,58 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>This structure allows developing, deploying, and scaling each service autonomously, facilitating maintenance, flexibility, and the evolution of the system.</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>Microservices</t>
-        </is>
-      </c>
+          <t>The application follows the Client-Server pattern which organizes the code into two differentiated components: the client and the server. This separation of responsibilities allows the client to focus on presentation and user experience, while the server focuses on business logic, security, data integrity, and persistence.</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>P_02</t>
+          <t>P_01</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>61</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>Each microservice is deployed independently, which allows updates, scaling and maintenance without affecting the rest of the system. It also allows each service to have its own programming language, database and environment. This flexibility facilitates adaptation to change and scalability of the application and improves the resilience of the system, since an error in a microservice does not mean the complete collapse of the application.</t>
+          <t>This separation of responsibilities allows [...] the server to focus on business logic, security, data integrity, and persistence.</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>CF_M05_C07 , *CF_M05_C10, *CF_M05_C18</t>
+          <t>CF_M05_C09 , *CF_M05_C16, *CF_M05_C17</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>CF_M05_P01</t>
+          <t>CF_M05_P02</t>
         </is>
       </c>
       <c r="U3" t="n">
-        <v>56</v>
+        <v>61</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>AD_02</t>
+          <t>AD_01</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>CF_M05_AD06</t>
+          <t>CF_M05_AD01</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.9115</v>
+        <v>0.857</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F4" t="n">
         <v>1</v>
@@ -1173,87 +1173,87 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J4" t="n">
         <v>1</v>
       </c>
       <c r="K4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="M4" t="n">
+        <v>1</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>The use of this architecture allows high scalability, availability, and accessibility, as resource management can be done according to needs and anywhere with an Internet connection.</t>
+          <t>This structure allows developing, deploying, and scaling each service autonomously, facilitating maintenance, flexibility, and the evolution of the system.</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Cloud computing</t>
+          <t>Microservices</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>AU_17, AU_18, AU_19</t>
+          <t>P_02</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>9</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>The use of this type of architecture allows high scalability, availability and accessibility, since resource management can be done according to needs and anywhere with an Internet connection. It also reduces maintainability, managed by resource providers, and without major expenses, since you pay for the resources consumed.</t>
+          <t>Each microservice is deployed independently, which allows updates, scaling and maintenance without affecting the rest of the system. It also allows each service to have its own programming language, database and environment. This flexibility facilitates adaptation to change and scalability of the application and improves the resilience of the system, since an error in a microservice does not mean the complete collapse of the application.</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>CF_M05_C06, CF_M05_C07, CF_M05_C08, *CF_M05_C18</t>
+          <t>CF_M05_C07 , *CF_M05_C10, *CF_M05_C18</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>CF_M05_P05</t>
+          <t>CF_M05_P01</t>
         </is>
       </c>
       <c r="U4" t="n">
-        <v>60</v>
+        <v>56</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>AD_03</t>
+          <t>AD_05</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>CF_M05_AD08</t>
+          <t>CF_M05_AD04</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.9245</v>
+        <v>0.8692</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F5" t="n">
-        <v>1</v>
-      </c>
-      <c r="G5" t="n">
         <v>0</v>
       </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="H5" t="inlineStr">
         <is>
           <t>-</t>
@@ -1272,45 +1272,124 @@
         <v>1</v>
       </c>
       <c r="M5" t="n">
-        <v>1</v>
+        <v>0.8605</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>This separation of responsibilities allows the client to focus on presentation and user experience, while the server focuses on business logic, security, data integrity, and persistence.</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>Client-Server</t>
-        </is>
-      </c>
+          <t>The Access Control microservice has as its main objective the management of user authentication and their permissions within the application. This microservice is essential to maintain the confidentiality and protection of data.</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>P_01</t>
+          <t>AU_10</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>58</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>This separation of responsibilities allows [...] the server to focus on business logic, security, data integrity, and persistence.</t>
+          <t>This microservice is essential for maintaining data confidentiality and protection.</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>CF_M05_C09 , *CF_M05_C16, *CF_M05_C17</t>
+          <t>*CF_M05_C11</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>CF_M05_P02</t>
+          <t>CF_M05_AU03</t>
         </is>
       </c>
       <c r="U5" t="n">
-        <v>61</v>
+        <v>58</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>AD_06</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>CF_M05_AD05</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>0.8985</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J6" t="n">
+        <v>1</v>
+      </c>
+      <c r="K6" t="n">
+        <v>1</v>
+      </c>
+      <c r="L6" t="n">
+        <v>1</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0.9106</v>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>The Communication Log microservice has as its main purpose to record all communications that occur within the system. This component acts as a mechanism for traceability and auditing, ensuring that each interaction is documented for subsequent analysis, incident resolution, and regulatory compliance.</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>AU_11</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>This component acts as a traceability and audit mechanism, ensuring that each interaction is documented for later analysis, incident resolution and regulatory compliance.</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>*CF_M05_C13</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>CF_M05_AU04</t>
+        </is>
+      </c>
+      <c r="U6" t="n">
+        <v>58</v>
       </c>
     </row>
   </sheetData>
@@ -1324,7 +1403,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1367,70 +1446,155 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AD_04</t>
+          <t>AD_03</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Angular applies the MVVM pattern, as its architecture is based on components and services.</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>MVVM</t>
-        </is>
-      </c>
+          <t>This microservice has the main function of routing all communications to the corresponding microservice within the system architecture.</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>P_03</t>
+          <t>AU_08</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>57</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>CF_M05_AD10</t>
+          <t>CF_M05_AD04</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>0.6804</v>
+        <v>0.7113</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AD_05</t>
+          <t>AD_04</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
+          <t>The portal microservice incorporates the binaries necessary for the frontEnd [...] of the rest of the applications of the portal. This ensures that the presentation layer is available and updated, facilitating deployment and reducing dependence on external elements.</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>AU_09</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>CF_M05_AD03</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>0.7473</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>AD_07</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>This microservice has as its main function the planning and programming of processes within the system.</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>AU_12</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>CF_M05_AD01</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>0.6771</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>AD_09</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Angular applies the MVVM (Model-View-ViewModel) pattern, as its architecture is based on components and services.</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>P_03</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>CF_M05_AD10</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>0.6768999999999999</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>AD_10</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
           <t>Spring Boot organizes the code following the layered pattern with which responsibilities are separated.</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Layered Architecture</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr">
         <is>
           <t>P_04</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>68</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>CF_M05_AD12</t>
         </is>
       </c>
-      <c r="G3" t="n">
+      <c r="G6" t="n">
         <v>0.7287</v>
       </c>
     </row>
@@ -1445,7 +1609,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1515,7 +1679,7 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>0.6653</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="3">
@@ -1544,135 +1708,135 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>AD_02</t>
+          <t>AD_04</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>0.6857</v>
+        <v>0.7473</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>CF_M05_AD04</t>
+          <t>CF_M05_AD07</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>This microservice is essential for maintaining data confidentiality and protection.</t>
+          <t>This separation of responsibilities allows the client to focus on presentation and user experience.</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>*CF_M05_C11</t>
+          <t>*CF_M05_C15</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>CF_M05_AU03</t>
+          <t>CF_M05_P02</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>AD_03</t>
+          <t>AD_08</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>0.6688</v>
+        <v>0.8127</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>CF_M05_AD05</t>
+          <t>CF_M05_AD09</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>This component acts as a traceability and audit mechanism, ensuring that each interaction is documented for later analysis, incident resolution and regulatory compliance.</t>
+          <t xml:space="preserve"> It allows you to create dynamic, interactive and scalable user interfaces, facilitating the development and maintenance of large applications.</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>*CF_M05_C13</t>
+          <t>CF_M05_C07, *CF_M05_C14, *CF_M05_C18</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>CF_M05_AU04</t>
+          <t>CF_M05_AU30</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>58</v>
+        <v>76</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>AD_03</t>
+          <t>AD_01</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>0.6309</v>
+        <v>0.7176</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>CF_M05_AD07</t>
+          <t>CF_M05_AD10</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>This separation of responsibilities allows the client to focus on presentation and user experience.</t>
+          <t>When making the decision to use Angular for frontEnd development and Spring for the backEnd, several technological criteria were considered, the work methodology that would be implemented throughout the development of the application was thought about and the long-term maintainability of the project was taken into consideration.</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>*CF_M05_C15</t>
+          <t>*CF_M05_C14</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>CF_M05_P02</t>
+          <t>CF_M05_AU30, CF_M05_AU29</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>61</v>
+        <v>77</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>AD_03</t>
+          <t>AD_09</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>0.8676</v>
+        <v>0.6768999999999999</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>CF_M05_AD09</t>
+          <t>CF_M05_AD11</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t xml:space="preserve"> It allows you to create dynamic, interactive and scalable user interfaces, facilitating the development and maintenance of large applications.</t>
+          <t>It allows you to automate the deployment, scaling and management of applications running in containers, run thousands of containers on different servers and ensure high availability.</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>CF_M05_C07, *CF_M05_C14, *CF_M05_C18</t>
+          <t>CF_M05_C06, CF_M05_C07</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>CF_M05_AU30</t>
+          <t>CF_M05_AU07</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1680,18 +1844,18 @@
         </is>
       </c>
       <c r="G7" t="n">
-        <v>0.7176</v>
+        <v>0.76</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>CF_M05_AD10</t>
+          <t>CF_M05_AD12</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>When making the decision to use Angular for frontEnd development and Spring for the backEnd, several technological criteria were considered, the work methodology that would be implemented throughout the development of the application was thought about and the long-term maintainability of the project was taken into consideration.</t>
+          <t>This structure clarifies roles, avoids unnecessary coupling, and makes it easier to test, reuse, and maintain the code over time.</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1701,35 +1865,35 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>CF_M05_AU30, CF_M05_AU29</t>
+          <t>CF_M05_AU29</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>AD_04</t>
+          <t>AD_01</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>0.6804</v>
+        <v>0.7494</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>CF_M05_AD11</t>
+          <t>CF_M05_AD13</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>It allows you to automate the deployment, scaling and management of applications running in containers, run thousands of containers on different servers and ensure high availability.</t>
+          <t>This diversity makes it easy to adapt to the needs of the project, allows the project to grow and scale in an agile manner and eliminates the need to look for other platforms when requirements evolve.</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>CF_M05_C06, CF_M05_C07</t>
+          <t>*CF_M05_C18</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1738,48 +1902,15 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>AD_02</t>
+          <t>AD_01</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>0.7877999999999999</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>CF_M05_AD12</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>This structure clarifies roles, avoids unnecessary coupling, and makes it easier to test, reuse, and maintain the code over time.</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>*CF_M05_C14</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>CF_M05_AU29</t>
-        </is>
-      </c>
-      <c r="E10" t="n">
-        <v>78</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>AD_01</t>
-        </is>
-      </c>
-      <c r="G10" t="n">
-        <v>0.7494</v>
+        <v>0.767</v>
       </c>
     </row>
   </sheetData>
